--- a/output/graficos_dimensiones/comunal_d_depmay_a_2019_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_d_depmay_a_2019_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-28 01:38</t>
+    <t xml:space="preserve">2026-08-17 20:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_depmay_a_2019_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_d_depmay_a_2019_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-17 20:28</t>
+    <t xml:space="preserve">2026-09-01 17:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_depmay_a_2019_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_d_depmay_a_2019_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-01 17:39</t>
+    <t xml:space="preserve">2026-09-06 22:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
